--- a/_other/ws_list.xlsx
+++ b/_other/ws_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713D7D88-6D25-46EB-8C5B-377B141FF84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53587C3B-DADC-4D8E-86F6-8A0442BDFB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
   <si>
     <t>номер</t>
   </si>
@@ -110,6 +110,45 @@
   </si>
   <si>
     <t>Парный реверс грид по DC</t>
+  </si>
+  <si>
+    <t>LWS2_SWIMIGSON</t>
+  </si>
+  <si>
+    <t>LWS2_PSGSON</t>
+  </si>
+  <si>
+    <t>LWS3_NEXUS</t>
+  </si>
+  <si>
+    <t>LWS3_APEX</t>
+  </si>
+  <si>
+    <t>LWS4_SWATR</t>
+  </si>
+  <si>
+    <t>Парный реверс хедж RSI</t>
+  </si>
+  <si>
+    <t>Плавающий грид-бот c ATR</t>
+  </si>
+  <si>
+    <t>LWS5_ARCHIMEDES</t>
+  </si>
+  <si>
+    <t>LWS5_CADUCEUS</t>
+  </si>
+  <si>
+    <t>Улучшенный  LWS1_FIRSTGRID</t>
+  </si>
+  <si>
+    <t>Улучшенный  LWS1_AUTOGRID</t>
+  </si>
+  <si>
+    <t>LWS6_TIDAL</t>
+  </si>
+  <si>
+    <t>LWS5_CADUCEUS с выходом по RSI</t>
   </si>
 </sst>
 </file>
@@ -181,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -190,6 +229,12 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -618,40 +663,136 @@
       <c r="A9">
         <v>8</v>
       </c>
+      <c r="B9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45979</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1">
+        <v>45979</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
+      <c r="B11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45979</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
+      <c r="B12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45979</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
+      <c r="B13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45984</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
+      <c r="B14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="1">
+        <v>45985</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
+      <c r="B15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="1">
+        <v>45985</v>
+      </c>
+      <c r="D15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="1">
+        <v>45985</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">

--- a/_other/ws_list.xlsx
+++ b/_other/ws_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53587C3B-DADC-4D8E-86F6-8A0442BDFB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7A474C-7110-43DB-90F7-BFACCD85D98F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
   <si>
     <t>номер</t>
   </si>
@@ -149,6 +149,12 @@
   </si>
   <si>
     <t>LWS5_CADUCEUS с выходом по RSI</t>
+  </si>
+  <si>
+    <t>LWS5_PROGRESSO</t>
+  </si>
+  <si>
+    <t>x-усредняющий грид-бот c авто рассчетом</t>
   </si>
 </sst>
 </file>
@@ -520,7 +526,7 @@
   <cols>
     <col min="2" max="2" width="22.5703125" customWidth="1"/>
     <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="36.42578125" customWidth="1"/>
+    <col min="4" max="4" width="45.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -795,82 +801,94 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="1">
+        <v>45999</v>
+      </c>
+      <c r="D17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>

--- a/_other/ws_list.xlsx
+++ b/_other/ws_list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\dev\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7A474C-7110-43DB-90F7-BFACCD85D98F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8A0AE3-1C36-4BC7-BBAB-9AD6EC70975A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="44">
   <si>
     <t>номер</t>
   </si>
@@ -155,6 +155,18 @@
   </si>
   <si>
     <t>x-усредняющий грид-бот c авто рассчетом</t>
+  </si>
+  <si>
+    <t>LWS7_FLOATGRESSO</t>
+  </si>
+  <si>
+    <t>плавающий x-усредняющий грид-бот</t>
+  </si>
+  <si>
+    <t>LWS5_XPG</t>
+  </si>
+  <si>
+    <t>ИСП1 LWS5_PROGRESSO</t>
   </si>
 </sst>
 </file>
@@ -522,14 +534,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E354"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="22.5703125" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="45.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.54296875" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" customWidth="1"/>
+    <col min="4" max="4" width="45.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -546,7 +558,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -563,7 +575,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -580,7 +592,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -597,7 +609,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -614,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -631,7 +643,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -648,7 +660,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -665,7 +677,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -682,7 +694,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -699,7 +711,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -716,7 +728,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -733,7 +745,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -750,7 +762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -767,7 +779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -784,7 +796,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -801,7 +813,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -818,1687 +830,1711 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="1">
+        <v>46000</v>
+      </c>
+      <c r="D18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="1">
+        <v>46000</v>
+      </c>
+      <c r="D19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>154</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>159</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>160</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>161</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>162</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>163</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>164</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>177</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>178</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>179</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>180</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>181</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>182</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>183</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>184</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>185</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>186</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>188</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>190</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>191</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>192</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>193</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>194</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>195</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>196</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>197</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>198</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>199</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>200</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>201</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>202</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>203</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>204</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>205</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>206</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>207</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>208</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>209</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>210</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>211</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>212</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>213</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>214</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>215</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>216</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>217</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>218</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>219</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>220</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>221</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>222</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>223</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>224</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>225</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>226</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>227</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>228</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>229</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>230</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>231</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>232</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>233</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>234</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>235</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>236</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>237</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>238</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>239</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>240</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>241</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>242</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>243</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>244</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>245</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>246</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>247</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>248</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>249</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>250</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>251</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>252</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>253</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>254</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>255</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>256</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>257</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>258</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>259</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>260</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>261</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>262</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A264">
         <v>263</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A265">
         <v>264</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A266">
         <v>265</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>266</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>267</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>268</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>269</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>270</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>271</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>272</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>273</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>274</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>275</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>276</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>277</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>278</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>279</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>280</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>281</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>282</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>283</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>284</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A286">
         <v>285</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A287">
         <v>286</v>
       </c>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A288">
         <v>287</v>
       </c>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>288</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>289</v>
       </c>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>290</v>
       </c>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>291</v>
       </c>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A293">
         <v>292</v>
       </c>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A294">
         <v>293</v>
       </c>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A295">
         <v>294</v>
       </c>
     </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A296">
         <v>295</v>
       </c>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A297">
         <v>296</v>
       </c>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A298">
         <v>297</v>
       </c>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A299">
         <v>298</v>
       </c>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A300">
         <v>299</v>
       </c>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A301">
         <v>300</v>
       </c>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A302">
         <v>301</v>
       </c>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A303">
         <v>302</v>
       </c>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A304">
         <v>303</v>
       </c>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A305">
         <v>304</v>
       </c>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A306">
         <v>305</v>
       </c>
     </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A307">
         <v>306</v>
       </c>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>307</v>
       </c>
     </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A309">
         <v>308</v>
       </c>
     </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>309</v>
       </c>
     </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A311">
         <v>310</v>
       </c>
     </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A312">
         <v>311</v>
       </c>
     </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>312</v>
       </c>
     </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A314">
         <v>313</v>
       </c>
     </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A315">
         <v>314</v>
       </c>
     </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A316">
         <v>315</v>
       </c>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A317">
         <v>316</v>
       </c>
     </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A318">
         <v>317</v>
       </c>
     </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A319">
         <v>318</v>
       </c>
     </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A320">
         <v>319</v>
       </c>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A321">
         <v>320</v>
       </c>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A322">
         <v>321</v>
       </c>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A323">
         <v>322</v>
       </c>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A324">
         <v>323</v>
       </c>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A325">
         <v>324</v>
       </c>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A326">
         <v>325</v>
       </c>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A327">
         <v>326</v>
       </c>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A328">
         <v>327</v>
       </c>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A329">
         <v>328</v>
       </c>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A330">
         <v>329</v>
       </c>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A331">
         <v>330</v>
       </c>
     </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A332">
         <v>331</v>
       </c>
     </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A333">
         <v>332</v>
       </c>
     </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A334">
         <v>333</v>
       </c>
     </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A335">
         <v>334</v>
       </c>
     </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A336">
         <v>335</v>
       </c>
     </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A337">
         <v>336</v>
       </c>
     </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A338">
         <v>337</v>
       </c>
     </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A339">
         <v>338</v>
       </c>
     </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A340">
         <v>339</v>
       </c>
     </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A341">
         <v>340</v>
       </c>
     </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A342">
         <v>341</v>
       </c>
     </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A343">
         <v>342</v>
       </c>
     </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A344">
         <v>343</v>
       </c>
     </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A345">
         <v>344</v>
       </c>
     </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A346">
         <v>345</v>
       </c>
     </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A347">
         <v>346</v>
       </c>
     </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A348">
         <v>347</v>
       </c>
     </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A349">
         <v>348</v>
       </c>
     </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A350">
         <v>349</v>
       </c>
     </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A351">
         <v>350</v>
       </c>
     </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A352">
         <v>351</v>
       </c>
     </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A353">
         <v>352</v>
       </c>
     </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A354">
         <v>353</v>
       </c>
@@ -2512,34 +2548,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B80973B1-AE11-4B5B-8085-60AFD0B6AEEF}">
   <dimension ref="A2:A7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>

--- a/_other/ws_list.xlsx
+++ b/_other/ws_list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\dev\RichLaughter2\_other\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8A0AE3-1C36-4BC7-BBAB-9AD6EC70975A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF74170-8DF1-4E28-8DB0-5C183B1E3F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="48">
   <si>
     <t>номер</t>
   </si>
@@ -167,6 +167,18 @@
   </si>
   <si>
     <t>ИСП1 LWS5_PROGRESSO</t>
+  </si>
+  <si>
+    <t>LWS5_EUCLID</t>
+  </si>
+  <si>
+    <t>грид-бот ИСП1 LWS5_ARCHIMEDES</t>
+  </si>
+  <si>
+    <t>LWS5_MERCATUS</t>
+  </si>
+  <si>
+    <t>ИСП1 LWS5_CADUCEUS</t>
   </si>
 </sst>
 </file>
@@ -534,14 +546,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E354"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.54296875" customWidth="1"/>
-    <col min="3" max="3" width="13.54296875" customWidth="1"/>
-    <col min="4" max="4" width="45.81640625" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="45.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +570,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -575,7 +587,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -592,7 +604,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -609,7 +621,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -626,7 +638,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -643,7 +655,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -660,7 +672,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -677,7 +689,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -694,7 +706,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -711,7 +723,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -728,7 +740,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -745,7 +757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -762,7 +774,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -779,7 +791,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -796,7 +808,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -813,7 +825,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -830,7 +842,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -847,7 +859,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -864,1677 +876,1701 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="1">
+        <v>46008</v>
+      </c>
+      <c r="D20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="1">
+        <v>46008</v>
+      </c>
+      <c r="D21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>202</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>207</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>208</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>210</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>212</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>217</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>220</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>221</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>222</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>223</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>224</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>225</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>226</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>227</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>228</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>229</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>230</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>231</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>232</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>233</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>234</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>235</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>237</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>242</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>244</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>245</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>246</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>247</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>248</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>249</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>250</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>251</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>252</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>253</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>254</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>255</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>256</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>257</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>258</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>259</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>260</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>261</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>262</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>263</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>264</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>265</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>266</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>267</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>268</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>269</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>270</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>271</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>272</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>273</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>274</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>275</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>276</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>277</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>278</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>279</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>280</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>281</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>282</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>283</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>284</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>285</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>286</v>
       </c>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>287</v>
       </c>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>288</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>289</v>
       </c>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>290</v>
       </c>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>291</v>
       </c>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>292</v>
       </c>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>293</v>
       </c>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>294</v>
       </c>
     </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>295</v>
       </c>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>296</v>
       </c>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>297</v>
       </c>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>298</v>
       </c>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>299</v>
       </c>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>300</v>
       </c>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>301</v>
       </c>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>302</v>
       </c>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>303</v>
       </c>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>304</v>
       </c>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>305</v>
       </c>
     </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>306</v>
       </c>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>307</v>
       </c>
     </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>308</v>
       </c>
     </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>309</v>
       </c>
     </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>310</v>
       </c>
     </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>311</v>
       </c>
     </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>312</v>
       </c>
     </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>313</v>
       </c>
     </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>314</v>
       </c>
     </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>315</v>
       </c>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>316</v>
       </c>
     </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>317</v>
       </c>
     </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>318</v>
       </c>
     </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>319</v>
       </c>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>320</v>
       </c>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>321</v>
       </c>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>322</v>
       </c>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>323</v>
       </c>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>324</v>
       </c>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>325</v>
       </c>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>326</v>
       </c>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>327</v>
       </c>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>328</v>
       </c>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>329</v>
       </c>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>330</v>
       </c>
     </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>331</v>
       </c>
     </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>332</v>
       </c>
     </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>333</v>
       </c>
     </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>334</v>
       </c>
     </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>335</v>
       </c>
     </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>336</v>
       </c>
     </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>337</v>
       </c>
     </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>338</v>
       </c>
     </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>339</v>
       </c>
     </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>340</v>
       </c>
     </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>341</v>
       </c>
     </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>342</v>
       </c>
     </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>343</v>
       </c>
     </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>344</v>
       </c>
     </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>345</v>
       </c>
     </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>346</v>
       </c>
     </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>347</v>
       </c>
     </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>348</v>
       </c>
     </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>349</v>
       </c>
     </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>350</v>
       </c>
     </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>351</v>
       </c>
     </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>352</v>
       </c>
     </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>353</v>
       </c>
@@ -2548,34 +2584,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B80973B1-AE11-4B5B-8085-60AFD0B6AEEF}">
   <dimension ref="A2:A7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>

--- a/_other/ws_list.xlsx
+++ b/_other/ws_list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\dev\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF74170-8DF1-4E28-8DB0-5C183B1E3F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{127B1134-7C9E-4689-8AFE-61980A8B23DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="52">
   <si>
     <t>номер</t>
   </si>
@@ -179,6 +179,18 @@
   </si>
   <si>
     <t>ИСП1 LWS5_CADUCEUS</t>
+  </si>
+  <si>
+    <t>PWS2_DIRDC</t>
+  </si>
+  <si>
+    <t>PWS2_DIRATR</t>
+  </si>
+  <si>
+    <t>направленный DDC</t>
+  </si>
+  <si>
+    <t>направленный ATR</t>
   </si>
 </sst>
 </file>
@@ -546,14 +558,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E354"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="22.5703125" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="45.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.54296875" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" customWidth="1"/>
+    <col min="4" max="4" width="45.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -570,7 +582,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -587,7 +599,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -604,7 +616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -621,7 +633,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -638,7 +650,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -655,7 +667,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -672,7 +684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -689,7 +701,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -706,7 +718,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -723,7 +735,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -740,7 +752,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -757,7 +769,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -774,7 +786,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -791,7 +803,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -808,7 +820,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -825,7 +837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -842,7 +854,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -859,7 +871,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -876,7 +888,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -893,7 +905,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -910,1667 +922,1691 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="1">
+        <v>46014</v>
+      </c>
+      <c r="D22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="1">
+        <v>46014</v>
+      </c>
+      <c r="D23" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>154</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>159</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>160</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>161</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>162</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>163</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>164</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>177</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>178</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>179</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>180</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>181</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>182</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>183</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>184</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>185</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>186</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>188</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>190</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>191</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>192</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>193</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>194</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>195</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>196</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>197</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>198</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>199</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>200</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>201</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>202</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>203</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>204</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>205</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>206</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>207</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>208</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>209</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>210</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>211</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>212</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>213</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>214</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>215</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>216</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>217</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>218</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>219</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>220</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>221</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>222</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>223</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>224</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>225</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>226</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>227</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>228</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>229</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>230</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>231</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>232</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>233</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>234</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>235</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>236</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>237</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>238</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>239</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>240</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>241</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>242</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>243</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>244</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>245</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>246</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>247</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>248</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>249</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>250</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>251</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>252</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>253</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>254</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>255</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>256</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>257</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>258</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>259</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>260</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>261</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>262</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A264">
         <v>263</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A265">
         <v>264</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A266">
         <v>265</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>266</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>267</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>268</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>269</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>270</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>271</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>272</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>273</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>274</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>275</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>276</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>277</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>278</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>279</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>280</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>281</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>282</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>283</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>284</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A286">
         <v>285</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A287">
         <v>286</v>
       </c>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A288">
         <v>287</v>
       </c>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>288</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>289</v>
       </c>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>290</v>
       </c>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>291</v>
       </c>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A293">
         <v>292</v>
       </c>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A294">
         <v>293</v>
       </c>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A295">
         <v>294</v>
       </c>
     </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A296">
         <v>295</v>
       </c>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A297">
         <v>296</v>
       </c>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A298">
         <v>297</v>
       </c>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A299">
         <v>298</v>
       </c>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A300">
         <v>299</v>
       </c>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A301">
         <v>300</v>
       </c>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A302">
         <v>301</v>
       </c>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A303">
         <v>302</v>
       </c>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A304">
         <v>303</v>
       </c>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A305">
         <v>304</v>
       </c>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A306">
         <v>305</v>
       </c>
     </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A307">
         <v>306</v>
       </c>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>307</v>
       </c>
     </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A309">
         <v>308</v>
       </c>
     </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>309</v>
       </c>
     </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A311">
         <v>310</v>
       </c>
     </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A312">
         <v>311</v>
       </c>
     </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>312</v>
       </c>
     </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A314">
         <v>313</v>
       </c>
     </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A315">
         <v>314</v>
       </c>
     </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A316">
         <v>315</v>
       </c>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A317">
         <v>316</v>
       </c>
     </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A318">
         <v>317</v>
       </c>
     </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A319">
         <v>318</v>
       </c>
     </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A320">
         <v>319</v>
       </c>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A321">
         <v>320</v>
       </c>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A322">
         <v>321</v>
       </c>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A323">
         <v>322</v>
       </c>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A324">
         <v>323</v>
       </c>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A325">
         <v>324</v>
       </c>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A326">
         <v>325</v>
       </c>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A327">
         <v>326</v>
       </c>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A328">
         <v>327</v>
       </c>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A329">
         <v>328</v>
       </c>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A330">
         <v>329</v>
       </c>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A331">
         <v>330</v>
       </c>
     </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A332">
         <v>331</v>
       </c>
     </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A333">
         <v>332</v>
       </c>
     </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A334">
         <v>333</v>
       </c>
     </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A335">
         <v>334</v>
       </c>
     </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A336">
         <v>335</v>
       </c>
     </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A337">
         <v>336</v>
       </c>
     </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A338">
         <v>337</v>
       </c>
     </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A339">
         <v>338</v>
       </c>
     </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A340">
         <v>339</v>
       </c>
     </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A341">
         <v>340</v>
       </c>
     </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A342">
         <v>341</v>
       </c>
     </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A343">
         <v>342</v>
       </c>
     </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A344">
         <v>343</v>
       </c>
     </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A345">
         <v>344</v>
       </c>
     </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A346">
         <v>345</v>
       </c>
     </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A347">
         <v>346</v>
       </c>
     </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A348">
         <v>347</v>
       </c>
     </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A349">
         <v>348</v>
       </c>
     </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A350">
         <v>349</v>
       </c>
     </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A351">
         <v>350</v>
       </c>
     </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A352">
         <v>351</v>
       </c>
     </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A353">
         <v>352</v>
       </c>
     </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A354">
         <v>353</v>
       </c>
@@ -2584,34 +2620,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B80973B1-AE11-4B5B-8085-60AFD0B6AEEF}">
   <dimension ref="A2:A7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>

--- a/_other/ws_list.xlsx
+++ b/_other/ws_list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\dev\RichLaughter2\_other\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{127B1134-7C9E-4689-8AFE-61980A8B23DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CFD4CBB-B1F8-4F13-917A-986A0DC905EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="56">
   <si>
     <t>номер</t>
   </si>
@@ -191,6 +191,18 @@
   </si>
   <si>
     <t>направленный ATR</t>
+  </si>
+  <si>
+    <t>SCAWS2_SHARKNADO</t>
+  </si>
+  <si>
+    <t>OpenWSCondition</t>
+  </si>
+  <si>
+    <t>Бот по зебре от sma на процент</t>
+  </si>
+  <si>
+    <t>Открытие позиции по условию цены</t>
   </si>
 </sst>
 </file>
@@ -262,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -275,6 +287,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -558,14 +576,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E354"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.54296875" customWidth="1"/>
-    <col min="3" max="3" width="13.54296875" customWidth="1"/>
-    <col min="4" max="4" width="45.81640625" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="45.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -582,7 +600,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -599,7 +617,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -616,7 +634,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -633,7 +651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -650,7 +668,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -667,7 +685,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -684,7 +702,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -701,7 +719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -718,7 +736,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -735,7 +753,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -752,7 +770,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -769,7 +787,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -786,7 +804,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -803,7 +821,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -820,7 +838,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -837,7 +855,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -854,7 +872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -871,7 +889,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -888,7 +906,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -905,7 +923,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -922,7 +940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -939,7 +957,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -956,1657 +974,1681 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B24" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="1">
+        <v>46017</v>
+      </c>
+      <c r="D24" t="s">
+        <v>54</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B25" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="1">
+        <v>46017</v>
+      </c>
+      <c r="D25" t="s">
+        <v>55</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>202</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>207</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>208</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>210</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>212</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>217</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>220</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>221</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>222</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>223</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>224</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>225</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>226</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>227</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>228</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>229</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>230</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>231</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>232</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>233</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>234</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>235</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>237</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>242</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>244</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>245</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>246</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>247</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>248</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>249</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>250</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>251</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>252</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>253</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>254</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>255</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>256</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>257</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>258</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>259</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>260</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>261</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>262</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>263</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>264</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>265</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>266</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>267</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>268</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>269</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>270</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>271</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>272</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>273</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>274</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>275</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>276</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>277</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>278</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>279</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>280</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>281</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>282</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>283</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>284</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>285</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>286</v>
       </c>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>287</v>
       </c>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>288</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>289</v>
       </c>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>290</v>
       </c>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>291</v>
       </c>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>292</v>
       </c>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>293</v>
       </c>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>294</v>
       </c>
     </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>295</v>
       </c>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>296</v>
       </c>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>297</v>
       </c>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>298</v>
       </c>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>299</v>
       </c>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>300</v>
       </c>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>301</v>
       </c>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>302</v>
       </c>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>303</v>
       </c>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>304</v>
       </c>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>305</v>
       </c>
     </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>306</v>
       </c>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>307</v>
       </c>
     </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>308</v>
       </c>
     </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>309</v>
       </c>
     </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>310</v>
       </c>
     </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>311</v>
       </c>
     </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>312</v>
       </c>
     </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>313</v>
       </c>
     </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>314</v>
       </c>
     </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>315</v>
       </c>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>316</v>
       </c>
     </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>317</v>
       </c>
     </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>318</v>
       </c>
     </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>319</v>
       </c>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>320</v>
       </c>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>321</v>
       </c>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>322</v>
       </c>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>323</v>
       </c>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>324</v>
       </c>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>325</v>
       </c>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>326</v>
       </c>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>327</v>
       </c>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>328</v>
       </c>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>329</v>
       </c>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>330</v>
       </c>
     </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>331</v>
       </c>
     </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>332</v>
       </c>
     </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>333</v>
       </c>
     </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>334</v>
       </c>
     </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>335</v>
       </c>
     </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>336</v>
       </c>
     </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>337</v>
       </c>
     </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>338</v>
       </c>
     </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>339</v>
       </c>
     </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>340</v>
       </c>
     </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>341</v>
       </c>
     </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>342</v>
       </c>
     </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>343</v>
       </c>
     </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>344</v>
       </c>
     </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>345</v>
       </c>
     </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>346</v>
       </c>
     </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>347</v>
       </c>
     </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>348</v>
       </c>
     </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>349</v>
       </c>
     </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>350</v>
       </c>
     </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>351</v>
       </c>
     </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>352</v>
       </c>
     </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>353</v>
       </c>
@@ -2620,34 +2662,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B80973B1-AE11-4B5B-8085-60AFD0B6AEEF}">
   <dimension ref="A2:A7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>

--- a/_other/ws_list.xlsx
+++ b/_other/ws_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CFD4CBB-B1F8-4F13-917A-986A0DC905EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CF6718-D2B5-40C5-9287-CFC31428568A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="58">
   <si>
     <t>номер</t>
   </si>
@@ -203,6 +203,12 @@
   </si>
   <si>
     <t>Открытие позиции по условию цены</t>
+  </si>
+  <si>
+    <t>LWS8_SINGULARITY</t>
+  </si>
+  <si>
+    <t>парный реверс грид-бот c хеджем</t>
   </si>
 </sst>
 </file>
@@ -1012,6 +1018,18 @@
       <c r="A26">
         <v>25</v>
       </c>
+      <c r="B26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="1">
+        <v>46019</v>
+      </c>
+      <c r="D26" t="s">
+        <v>57</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">

--- a/_other/ws_list.xlsx
+++ b/_other/ws_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CF6718-D2B5-40C5-9287-CFC31428568A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815BE3E5-F394-4920-A56E-C57A53253947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="60">
   <si>
     <t>номер</t>
   </si>
@@ -209,6 +209,12 @@
   </si>
   <si>
     <t>парный реверс грид-бот c хеджем</t>
+  </si>
+  <si>
+    <t>LWS8_GRAVITON</t>
+  </si>
+  <si>
+    <t>усредняющий парный реверс грид-бот c хеджем</t>
   </si>
 </sst>
 </file>
@@ -1035,6 +1041,18 @@
       <c r="A27">
         <v>26</v>
       </c>
+      <c r="B27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="1">
+        <v>46019</v>
+      </c>
+      <c r="D27" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">

--- a/_other/ws_list.xlsx
+++ b/_other/ws_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815BE3E5-F394-4920-A56E-C57A53253947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3253554D-1FEC-4635-85F6-B2A5B31463DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="62">
   <si>
     <t>номер</t>
   </si>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>усредняющий парный реверс грид-бот c хеджем</t>
+  </si>
+  <si>
+    <t>APSWS1_DYNAMO</t>
+  </si>
+  <si>
+    <t>Арбитраже со сбромов фандинга вечером</t>
   </si>
 </sst>
 </file>
@@ -625,7 +631,7 @@
       <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="7" t="s">
         <v>8</v>
       </c>
     </row>
@@ -642,7 +648,7 @@
       <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -659,7 +665,7 @@
       <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -676,7 +682,7 @@
       <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -693,7 +699,7 @@
       <c r="D6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -710,7 +716,7 @@
       <c r="D7" t="s">
         <v>23</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -727,7 +733,7 @@
       <c r="D8" t="s">
         <v>24</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -744,7 +750,7 @@
       <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -761,7 +767,7 @@
       <c r="D10" t="s">
         <v>23</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -778,7 +784,7 @@
       <c r="D11" t="s">
         <v>30</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -795,7 +801,7 @@
       <c r="D12" t="s">
         <v>30</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -812,7 +818,7 @@
       <c r="D13" t="s">
         <v>31</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -829,7 +835,7 @@
       <c r="D14" t="s">
         <v>34</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -846,7 +852,7 @@
       <c r="D15" t="s">
         <v>35</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -863,7 +869,7 @@
       <c r="D16" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -880,7 +886,7 @@
       <c r="D17" t="s">
         <v>39</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -897,7 +903,7 @@
       <c r="D18" t="s">
         <v>41</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -914,7 +920,7 @@
       <c r="D19" t="s">
         <v>43</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -931,7 +937,7 @@
       <c r="D20" t="s">
         <v>45</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -948,7 +954,7 @@
       <c r="D21" t="s">
         <v>47</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -965,7 +971,7 @@
       <c r="D22" t="s">
         <v>50</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -982,7 +988,7 @@
       <c r="D23" t="s">
         <v>51</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -999,7 +1005,7 @@
       <c r="D24" t="s">
         <v>54</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1016,7 +1022,7 @@
       <c r="D25" t="s">
         <v>55</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="7" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1033,7 +1039,7 @@
       <c r="D26" t="s">
         <v>57</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1050,13 +1056,25 @@
       <c r="D27" t="s">
         <v>59</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="1">
+        <v>46020</v>
+      </c>
+      <c r="D28" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">

--- a/_other/ws_list.xlsx
+++ b/_other/ws_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3253554D-1FEC-4635-85F6-B2A5B31463DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF62732-4F0B-4985-998C-388C525110BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="64">
   <si>
     <t>номер</t>
   </si>
@@ -221,6 +221,12 @@
   </si>
   <si>
     <t>Арбитраже со сбромов фандинга вечером</t>
+  </si>
+  <si>
+    <t>APSWS2_SPARTACUS</t>
+  </si>
+  <si>
+    <t>статистический арбитраж</t>
   </si>
 </sst>
 </file>
@@ -1081,6 +1087,18 @@
       <c r="A29">
         <v>28</v>
       </c>
+      <c r="B29" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="1">
+        <v>46021</v>
+      </c>
+      <c r="D29" t="s">
+        <v>63</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">

--- a/_other/ws_list.xlsx
+++ b/_other/ws_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF62732-4F0B-4985-998C-388C525110BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F0295E-75C4-4441-8EA7-900ED31D88DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="66">
   <si>
     <t>номер</t>
   </si>
@@ -227,6 +227,12 @@
   </si>
   <si>
     <t>статистический арбитраж</t>
+  </si>
+  <si>
+    <t>APSWS3_PROMETHEUS</t>
+  </si>
+  <si>
+    <t>сеточный статистический арбитраж</t>
   </si>
 </sst>
 </file>
@@ -1104,6 +1110,18 @@
       <c r="A30">
         <v>29</v>
       </c>
+      <c r="B30" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="1">
+        <v>46025</v>
+      </c>
+      <c r="D30" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">

--- a/_other/ws_list.xlsx
+++ b/_other/ws_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F0295E-75C4-4441-8EA7-900ED31D88DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843F9067-D8F3-4778-904A-9F1C3711099A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="68">
   <si>
     <t>номер</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>сеточный статистический арбитраж</t>
+  </si>
+  <si>
+    <t>LWS8_LITE</t>
+  </si>
+  <si>
+    <t>парный реверс одноуровневый бот c хеджем</t>
   </si>
 </sst>
 </file>
@@ -1127,6 +1133,18 @@
       <c r="A31">
         <v>30</v>
       </c>
+      <c r="B31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="1">
+        <v>46027</v>
+      </c>
+      <c r="D31" t="s">
+        <v>67</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
